--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N84_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N84_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.32433795173507</v>
+        <v>10.61520491715695</v>
       </c>
       <c r="D2" t="n">
-        <v>15.36379601266717</v>
+        <v>2.496616852058415</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
